--- a/data/trans_orig/Q46-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q46-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su peso</t>
+          <t>Población según su peso (tasa de respuesta: 97,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>77,08; 78,8</t>
+          <t>77,05; 78,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>79,3; 81,37</t>
+          <t>79,31; 81,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78,95; 81,05</t>
+          <t>78,96; 81,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79,84; 82,37</t>
+          <t>79,81; 82,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>65,12; 66,91</t>
+          <t>65,14; 66,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,42; 68,34</t>
+          <t>66,49; 68,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,4; 68,45</t>
+          <t>66,44; 68,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>69,44; 327,45</t>
+          <t>69,55; 325,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>71,28; 72,67</t>
+          <t>71,31; 72,73</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73,16; 74,78</t>
+          <t>73,06; 74,73</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72,86; 74,48</t>
+          <t>72,79; 74,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>75,2; 239,47</t>
+          <t>75,14; 240,05</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>78,25; 79,78</t>
+          <t>78,22; 79,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>79,13; 80,69</t>
+          <t>79,07; 80,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78,89; 80,86</t>
+          <t>78,92; 80,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79,7; 91,14</t>
+          <t>79,74; 91,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>65,02; 66,58</t>
+          <t>64,97; 66,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,54; 69,25</t>
+          <t>67,53; 69,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,38; 69,04</t>
+          <t>67,38; 69,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>67,36; 70,35</t>
+          <t>67,4; 70,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>71,75; 73,0</t>
+          <t>71,74; 72,99</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73,47; 74,76</t>
+          <t>73,5; 74,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73,33; 74,66</t>
+          <t>73,36; 74,68</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>73,94; 86,33</t>
+          <t>73,95; 85,49</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>76,4; 78,05</t>
+          <t>76,46; 78,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>78,32; 80,21</t>
+          <t>78,36; 80,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78,2; 80,27</t>
+          <t>78,25; 80,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>78,79; 81,49</t>
+          <t>78,73; 81,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64,9; 66,64</t>
+          <t>64,84; 66,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>67,52; 69,48</t>
+          <t>67,45; 69,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65,98; 67,99</t>
+          <t>66,04; 68,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>67,43; 76,35</t>
+          <t>67,55; 77,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>70,75; 72,11</t>
+          <t>70,82; 72,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>73,15; 74,6</t>
+          <t>73,07; 74,64</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72,24; 73,8</t>
+          <t>72,3; 73,9</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>73,7; 77,54</t>
+          <t>73,71; 77,66</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>76,79; 78,3</t>
+          <t>76,82; 78,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>79,12; 80,94</t>
+          <t>79,19; 80,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79,73; 81,45</t>
+          <t>79,72; 81,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79,81; 81,77</t>
+          <t>79,85; 81,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>64,11; 65,74</t>
+          <t>64,07; 65,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,96; 68,51</t>
+          <t>66,91; 68,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,84; 68,55</t>
+          <t>66,9; 68,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>65,63; 67,9</t>
+          <t>65,59; 67,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>70,32; 71,55</t>
+          <t>70,33; 71,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72,93; 74,25</t>
+          <t>72,96; 74,28</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73,24; 74,54</t>
+          <t>73,26; 74,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>71,74; 74,21</t>
+          <t>71,71; 74,14</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>77,56; 78,36</t>
+          <t>77,57; 78,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79,45; 80,33</t>
+          <t>79,4; 80,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79,51; 80,47</t>
+          <t>79,48; 80,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80,32; 86,05</t>
+          <t>80,3; 86,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>65,1; 65,97</t>
+          <t>65,11; 65,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,55; 68,43</t>
+          <t>67,54; 68,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,23; 68,13</t>
+          <t>67,22; 68,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>68,34; 129,69</t>
+          <t>68,42; 149,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>71,33; 71,99</t>
+          <t>71,35; 71,98</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73,52; 74,22</t>
+          <t>73,49; 74,21</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73,33; 74,1</t>
+          <t>73,32; 74,07</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>74,57; 105,93</t>
+          <t>74,75; 107,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q46-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q46-Habitat-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>81,15</t>
+          <t>81,02</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>134,91</t>
+          <t>70,82</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>109,65</t>
+          <t>75,78</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>77,05; 78,75</t>
+          <t>77,09; 78,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>79,31; 81,31</t>
+          <t>79,23; 81,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78,96; 81,1</t>
+          <t>78,96; 81,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79,81; 82,29</t>
+          <t>79,86; 82,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>65,14; 66,91</t>
+          <t>65,14; 66,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,49; 68,48</t>
+          <t>66,44; 68,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,44; 68,5</t>
+          <t>66,38; 68,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>69,55; 325,36</t>
+          <t>69,11; 74,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>71,31; 72,73</t>
+          <t>71,3; 72,7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73,06; 74,73</t>
+          <t>73,18; 74,7</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72,79; 74,5</t>
+          <t>72,85; 74,53</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>75,14; 240,05</t>
+          <t>74,74; 77,68</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>84,17</t>
+          <t>79,87</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>68,31</t>
+          <t>68,45</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>77,17</t>
+          <t>74,14</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>78,22; 79,84</t>
+          <t>78,23; 79,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>79,07; 80,71</t>
+          <t>79,12; 80,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78,92; 80,89</t>
+          <t>78,97; 80,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79,74; 91,32</t>
+          <t>78,93; 80,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>64,97; 66,45</t>
+          <t>64,96; 66,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,53; 69,21</t>
+          <t>67,47; 69,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,38; 69,07</t>
+          <t>67,44; 69,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>67,4; 70,31</t>
+          <t>67,56; 70,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>71,74; 72,99</t>
+          <t>71,72; 72,96</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73,5; 74,74</t>
+          <t>73,49; 74,78</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73,36; 74,68</t>
+          <t>73,36; 74,69</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>73,95; 85,49</t>
+          <t>73,45; 75,17</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80,08</t>
+          <t>80,18</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>71,17</t>
+          <t>67,89</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>75,1</t>
+          <t>74,02</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>76,46; 78,0</t>
+          <t>76,38; 78,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>78,36; 80,2</t>
+          <t>78,21; 80,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78,25; 80,31</t>
+          <t>78,29; 80,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>78,73; 81,31</t>
+          <t>79,04; 81,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64,84; 66,61</t>
+          <t>64,86; 66,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>67,45; 69,39</t>
+          <t>67,47; 69,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66,04; 68,12</t>
+          <t>66,06; 67,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>67,55; 77,56</t>
+          <t>67,07; 68,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>70,82; 72,16</t>
+          <t>70,78; 72,18</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>73,07; 74,64</t>
+          <t>73,11; 74,61</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72,3; 73,9</t>
+          <t>72,27; 73,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>73,71; 77,66</t>
+          <t>73,27; 74,86</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80,78</t>
+          <t>80,62</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>67,02</t>
+          <t>67,73</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>73,34</t>
+          <t>73,79</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>76,82; 78,34</t>
+          <t>76,83; 78,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>79,19; 80,87</t>
+          <t>79,18; 81,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79,72; 81,53</t>
+          <t>79,77; 81,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79,85; 81,87</t>
+          <t>79,72; 81,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>64,07; 65,7</t>
+          <t>64,11; 65,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,91; 68,55</t>
+          <t>66,86; 68,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,9; 68,63</t>
+          <t>66,85; 68,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>65,59; 67,92</t>
+          <t>66,89; 68,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>70,33; 71,58</t>
+          <t>70,34; 71,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72,96; 74,28</t>
+          <t>73,0; 74,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73,26; 74,65</t>
+          <t>73,19; 74,59</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>71,71; 74,14</t>
+          <t>73,17; 74,49</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>81,88</t>
+          <t>80,37</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>81,67</t>
+          <t>68,57</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>81,77</t>
+          <t>74,33</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>77,57; 78,36</t>
+          <t>77,55; 78,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79,4; 80,34</t>
+          <t>79,43; 80,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79,48; 80,41</t>
+          <t>79,44; 80,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80,3; 86,48</t>
+          <t>79,88; 80,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>65,11; 65,94</t>
+          <t>65,13; 65,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,54; 68,46</t>
+          <t>67,59; 68,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,22; 68,11</t>
+          <t>67,21; 68,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>68,42; 149,16</t>
+          <t>68,03; 69,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>71,35; 71,98</t>
+          <t>71,35; 72,0</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73,49; 74,21</t>
+          <t>73,5; 74,19</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73,32; 74,07</t>
+          <t>73,31; 74,06</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>74,75; 107,21</t>
+          <t>73,95; 74,9</t>
         </is>
       </c>
     </row>
